--- a/product_search/product_list.xlsx
+++ b/product_search/product_list.xlsx
@@ -45,6 +45,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>남녀공용이지만, 여자상품으로 여자코드사용
@@ -57,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="143">
   <si>
     <t>자체상품코드</t>
   </si>
@@ -645,10 +646,22 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>UOT0002</t>
+    <t>루즈핏 후드윈드브레이커 (4Color)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>루즈핏 후드윈드브레이커 (4Color)</t>
+    <t>UOT0003</t>
+  </si>
+  <si>
+    <t>UOT0002</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>세미크롭핏 스웨이드 블루종 자켓(4Color)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=77</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -656,7 +669,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -698,6 +711,7 @@
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -705,6 +719,13 @@
       <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -38477,19 +38498,25 @@
     </row>
     <row r="3" spans="1:3" ht="17.25" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
+      <c r="A4" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="5" spans="1:3" ht="17.25" customHeight="1">
       <c r="A5" s="2"/>
@@ -43476,9 +43503,10 @@
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1"/>
     <hyperlink ref="C3" r:id="rId2"/>
+    <hyperlink ref="C4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape" r:id="rId3"/>
+  <pageSetup orientation="landscape" r:id="rId4"/>
 </worksheet>
 </file>
 

--- a/product_search/product_list.xlsx
+++ b/product_search/product_list.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9108" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9108" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="상의" sheetId="1" r:id="rId1"/>
@@ -145,9 +145,6 @@
   </si>
   <si>
     <t>루즈핏 생지데님자켓 (2Color)</t>
-  </si>
-  <si>
-    <t>WBT0001</t>
   </si>
   <si>
     <t>https://bellroute.cafe24.com/product/detail.html?product_no=16</t>
@@ -664,6 +661,10 @@
     <t>https://bellroute.cafe24.com/product/detail.html?product_no=77</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
+  <si>
+    <t>WBT0010</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1048,73 +1049,73 @@
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>20</v>
-      </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
       <c r="A4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="C4" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1">
       <c r="A5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>35</v>
-      </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1">
       <c r="A6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="D6" s="2"/>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1">
       <c r="A7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>48</v>
-      </c>
       <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1">
       <c r="A8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>53</v>
       </c>
       <c r="D8" s="2"/>
     </row>
@@ -7105,18 +7106,18 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A2" s="2" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>135</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17.25" customHeight="1">
@@ -12143,156 +12144,156 @@
     </row>
     <row r="2" spans="1:3" ht="17.25" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>10</v>
+        <v>142</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="3" spans="1:3" ht="17.25" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="C3" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17.25" customHeight="1">
       <c r="A4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>38</v>
-      </c>
     </row>
     <row r="5" spans="1:3" ht="17.25" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>50</v>
-      </c>
     </row>
     <row r="6" spans="1:3" ht="17.25" customHeight="1">
       <c r="A6" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C6" s="4" t="s">
+    </row>
+    <row r="7" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A7" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C7" s="4" t="s">
+    </row>
+    <row r="8" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A8" s="2" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A8" s="2" t="s">
+      <c r="B8" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C8" s="4" t="s">
+    </row>
+    <row r="9" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A9" s="2" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A9" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="4" t="s">
+    </row>
+    <row r="10" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A10" s="2" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A10" s="2" t="s">
+      <c r="B10" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="4" t="s">
+    </row>
+    <row r="11" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A11" s="2" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A11" s="2" t="s">
+      <c r="B11" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C11" s="4" t="s">
+    </row>
+    <row r="12" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A12" s="2" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A12" s="2" t="s">
+      <c r="B12" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C12" s="4" t="s">
+    </row>
+    <row r="13" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A13" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A13" s="2" t="s">
+      <c r="B13" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="C13" s="4" t="s">
+    </row>
+    <row r="14" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A14" s="2" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A14" s="2" t="s">
+      <c r="B14" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C14" s="4" t="s">
+    </row>
+    <row r="15" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A15" s="2" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A15" s="2" t="s">
+      <c r="B15" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C15" s="4" t="s">
         <v>82</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="17.25" customHeight="1">
@@ -17239,8 +17240,8 @@
     <hyperlink ref="C15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
-  <legacyDrawing r:id="rId15"/>
+  <pageSetup orientation="landscape" r:id="rId15"/>
+  <legacyDrawing r:id="rId16"/>
 </worksheet>
 </file>
 
@@ -17274,40 +17275,40 @@
         <v>9</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17.25" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>23</v>
-      </c>
     </row>
     <row r="4" spans="1:3" ht="17.25" customHeight="1">
       <c r="A4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>32</v>
-      </c>
     </row>
     <row r="5" spans="1:3" ht="17.25" customHeight="1">
       <c r="A5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17.25" customHeight="1">
@@ -22317,18 +22318,18 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17.25" customHeight="1">
@@ -27350,29 +27351,29 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A2" s="2" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A2" s="2" t="s">
-        <v>85</v>
+      <c r="B2" s="2" t="s">
+        <v>86</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>88</v>
-      </c>
     </row>
     <row r="3" spans="1:3" ht="17.25" customHeight="1">
       <c r="A3" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17.25" customHeight="1">
@@ -32390,51 +32391,51 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:26" ht="17.25" customHeight="1">
       <c r="A2" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="4" t="s">
+    </row>
+    <row r="3" spans="1:26" ht="17.25" customHeight="1">
+      <c r="A3" s="2" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="3" spans="1:26" ht="17.25" customHeight="1">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>94</v>
-      </c>
     </row>
     <row r="4" spans="1:26" ht="17.25" customHeight="1">
       <c r="A4" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C4" s="4" t="s">
+    </row>
+    <row r="5" spans="1:26" ht="17.25" customHeight="1">
+      <c r="A5" s="5" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="5" spans="1:26" ht="17.25" customHeight="1">
-      <c r="A5" s="5" t="s">
+      <c r="B5" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>102</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>103</v>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
@@ -38482,40 +38483,40 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A2" s="1" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>107</v>
-      </c>
     </row>
     <row r="3" spans="1:3" ht="17.25" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A4" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A4" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="8" t="s">
         <v>141</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.25" customHeight="1">
@@ -43529,95 +43530,95 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A2" s="2" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="C2" s="4" t="s">
+    </row>
+    <row r="3" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A3" s="2" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="C3" s="4" t="s">
+    </row>
+    <row r="4" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A4" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C4" s="4" t="s">
+    </row>
+    <row r="5" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A5" s="2" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A5" s="2" t="s">
+      <c r="B5" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="C5" s="4" t="s">
+    </row>
+    <row r="6" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A6" s="2" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A6" s="2" t="s">
+      <c r="B6" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C6" s="4" t="s">
+    </row>
+    <row r="7" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A7" s="2" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A7" s="2" t="s">
+      <c r="B7" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C7" s="4" t="s">
+    </row>
+    <row r="8" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A8" s="2" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A8" s="2" t="s">
+      <c r="B8" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C8" s="4" t="s">
+    </row>
+    <row r="9" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A9" s="2" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A9" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="4" t="s">
         <v>131</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17.25" customHeight="1">

--- a/product_search/product_list.xlsx
+++ b/product_search/product_list.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9108" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9108" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="상의" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="144">
   <si>
     <t>자체상품코드</t>
   </si>
@@ -665,6 +665,10 @@
     <t>WBT0010</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
+  <si>
+    <t>UTP0005</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -32462,7 +32466,9 @@
       <c r="Z5" s="7"/>
     </row>
     <row r="6" spans="1:26" ht="17.25" customHeight="1">
-      <c r="A6" s="2"/>
+      <c r="A6" s="2" t="s">
+        <v>143</v>
+      </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
     </row>

--- a/product_search/product_list.xlsx
+++ b/product_search/product_list.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9108" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9108" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="상의" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="145">
   <si>
     <t>자체상품코드</t>
   </si>
@@ -667,6 +667,10 @@
   </si>
   <si>
     <t>UTP0005</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>UTR0009</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -43628,7 +43632,9 @@
       </c>
     </row>
     <row r="10" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A10" s="2"/>
+      <c r="A10" s="2" t="s">
+        <v>144</v>
+      </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
     </row>

--- a/product_search/product_list.xlsx
+++ b/product_search/product_list.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9108" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9108" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="상의" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="147">
   <si>
     <t>자체상품코드</t>
   </si>
@@ -673,6 +673,13 @@
     <t>UTR0009</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
+  <si>
+    <t>MBT0015</t>
+  </si>
+  <si>
+    <t>워싱 커브드진 (3Color)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -12305,8 +12312,12 @@
       </c>
     </row>
     <row r="16" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
+      <c r="A16" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>146</v>
+      </c>
       <c r="C16" s="2"/>
     </row>
     <row r="17" spans="1:3" ht="17.25" customHeight="1">

--- a/product_search/product_list.xlsx
+++ b/product_search/product_list.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9108" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9108" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="상의" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="155">
   <si>
     <t>자체상품코드</t>
   </si>
@@ -680,6 +680,38 @@
     <t>워싱 커브드진 (3Color)</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=81</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>MOT0005</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>스탠다드핏 빈티지 데님자켓</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=80</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>오버핏 체크남방셔츠 (4Color)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=78</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>[1+1할인] 벌룬핏 사이드 옆핀턱 나일론 바스락팬츠 (5Color)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=79</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -12318,7 +12350,9 @@
       <c r="B16" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C16" s="2"/>
+      <c r="C16" s="8" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="17" spans="1:3" ht="17.25" customHeight="1">
       <c r="A17" s="2"/>
@@ -17257,10 +17291,11 @@
     <hyperlink ref="C13" r:id="rId12"/>
     <hyperlink ref="C14" r:id="rId13"/>
     <hyperlink ref="C15" r:id="rId14"/>
+    <hyperlink ref="C16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape" r:id="rId15"/>
-  <legacyDrawing r:id="rId16"/>
+  <pageSetup orientation="landscape" r:id="rId16"/>
+  <legacyDrawing r:id="rId17"/>
 </worksheet>
 </file>
 
@@ -17331,9 +17366,15 @@
       </c>
     </row>
     <row r="6" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
+      <c r="A6" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="7" spans="1:3" ht="17.25" customHeight="1">
       <c r="A7" s="2"/>
@@ -22312,6 +22353,7 @@
     <hyperlink ref="C3" r:id="rId2"/>
     <hyperlink ref="C4" r:id="rId3"/>
     <hyperlink ref="C5" r:id="rId4"/>
+    <hyperlink ref="C6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -32484,8 +32526,12 @@
       <c r="A6" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
+      <c r="B6" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="7" spans="1:26" ht="17.25" customHeight="1">
       <c r="A7" s="2"/>
@@ -37464,6 +37510,7 @@
     <hyperlink ref="C3" r:id="rId2"/>
     <hyperlink ref="C4" r:id="rId3"/>
     <hyperlink ref="C5" r:id="rId4"/>
+    <hyperlink ref="C6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -43646,8 +43693,12 @@
       <c r="A10" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
+      <c r="B10" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="11" spans="1:3" ht="17.25" customHeight="1">
       <c r="A11" s="2"/>
@@ -48610,6 +48661,7 @@
     <hyperlink ref="C7" r:id="rId6"/>
     <hyperlink ref="C8" r:id="rId7"/>
     <hyperlink ref="C9" r:id="rId8"/>
+    <hyperlink ref="C10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>

--- a/product_search/product_list.xlsx
+++ b/product_search/product_list.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9108" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9108" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="상의" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="157">
   <si>
     <t>자체상품코드</t>
   </si>
@@ -712,6 +712,14 @@
     <t>https://bellroute.cafe24.com/product/detail.html?product_no=79</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
+  <si>
+    <t>UTP0006</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>오버핏 나그랑 긴팔티셔츠(5Color)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -32534,8 +32542,12 @@
       </c>
     </row>
     <row r="7" spans="1:26" ht="17.25" customHeight="1">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
+      <c r="A7" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>156</v>
+      </c>
       <c r="C7" s="2"/>
     </row>
     <row r="8" spans="1:26" ht="17.25" customHeight="1">

--- a/product_search/product_list.xlsx
+++ b/product_search/product_list.xlsx
@@ -41,39 +41,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="159">
   <si>
     <t>자체상품코드</t>
   </si>
   <si>
     <t>상품명</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Malgun Gothic"/>
-        <color rgb="FF000000"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve">상세페이지 </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="맑은 고딕"/>
-        <color rgb="FF000000"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>URL</t>
-    </r>
-  </si>
-  <si>
-    <t>MTP0001</t>
-  </si>
-  <si>
-    <t>여름 오버핏 린넨셔츠 (5Color)</t>
-  </si>
-  <si>
-    <t>https://bellroute.cafe24.com/product/detail.html?product_no=21</t>
   </si>
   <si>
     <r>
@@ -112,6 +85,24 @@
     </r>
   </si>
   <si>
+    <t>MTP0001</t>
+  </si>
+  <si>
+    <t>여름 오버핏 린넨셔츠 (5Color)</t>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=21</t>
+  </si>
+  <si>
+    <t>WBT0010</t>
+  </si>
+  <si>
+    <t>와이드핏 워싱 데님팬츠 (5Color)</t>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=11</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <rFont val="Malgun Gothic"/>
@@ -130,16 +121,34 @@
     </r>
   </si>
   <si>
-    <t>MTR0001</t>
-  </si>
-  <si>
-    <t>플레어핏 부츠컷팬츠 (2Color)</t>
+    <r>
+      <rPr>
+        <rFont val="Malgun Gothic"/>
+        <color rgb="FF000000"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t xml:space="preserve">상세페이지 </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="맑은 고딕"/>
+        <color rgb="FF000000"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t>URL</t>
+    </r>
   </si>
   <si>
     <t>MOT0001</t>
   </si>
   <si>
+    <t>MTR0001</t>
+  </si>
+  <si>
     <t>루즈핏 생지데님자켓 (2Color)</t>
+  </si>
+  <si>
+    <t>플레어핏 부츠컷팬츠 (2Color)</t>
   </si>
   <si>
     <t>https://bellroute.cafe24.com/product/detail.html?product_no=31</t>
@@ -148,28 +157,19 @@
     <t>https://bellroute.cafe24.com/product/detail.html?product_no=16</t>
   </si>
   <si>
-    <t>WBT0010</t>
+    <t>MTP0002</t>
   </si>
   <si>
-    <t>와이드핏 워싱 데님팬츠 (5Color)</t>
-  </si>
-  <si>
-    <t>https://bellroute.cafe24.com/product/detail.html?product_no=11</t>
-  </si>
-  <si>
-    <t>MTP0002</t>
+    <t>MBT0002</t>
   </si>
   <si>
     <t>[1+1 할인] 머슬핏 쿨링 반팔티셔츠 (6Color)</t>
   </si>
   <si>
-    <t>https://bellroute.cafe24.com/product/detail.html?product_no=28</t>
+    <t>세미와이드핏 슬랙스 (5Color)</t>
   </si>
   <si>
-    <t>MBT0002</t>
-  </si>
-  <si>
-    <t>세미와이드핏 슬랙스 (5Color)</t>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=28</t>
   </si>
   <si>
     <t>https://bellroute.cafe24.com/product/detail.html?product_no=12</t>
@@ -229,6 +229,15 @@
     <t>https://bellroute.cafe24.com/product/detail.html?product_no=14</t>
   </si>
   <si>
+    <t>MOT0004</t>
+  </si>
+  <si>
+    <t>크롭핏 하이넥 블루종집업 (3Color)</t>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=53</t>
+  </si>
+  <si>
     <t>MTP0005</t>
   </si>
   <si>
@@ -238,15 +247,6 @@
     <t>https://bellroute.cafe24.com/product/detail.html?product_no=51</t>
   </si>
   <si>
-    <t>MOT0004</t>
-  </si>
-  <si>
-    <t>크롭핏 하이넥 블루종집업 (3Color)</t>
-  </si>
-  <si>
-    <t>https://bellroute.cafe24.com/product/detail.html?product_no=53</t>
-  </si>
-  <si>
     <t>MBT0005</t>
   </si>
   <si>
@@ -254,6 +254,15 @@
   </si>
   <si>
     <t>https://bellroute.cafe24.com/product/detail.html?product_no=15</t>
+  </si>
+  <si>
+    <t>MOT0005</t>
+  </si>
+  <si>
+    <t>스탠다드핏 빈티지 데님자켓</t>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=80</t>
   </si>
   <si>
     <t>MTP0006</t>
@@ -268,19 +277,10 @@
     <t>MBT0006</t>
   </si>
   <si>
-    <t>MOT0005</t>
-  </si>
-  <si>
     <t>벌룬핏 코듀로이 카고팬츠 (3Color)</t>
   </si>
   <si>
-    <t>스탠다드핏 빈티지 데님자켓</t>
-  </si>
-  <si>
     <t>https://bellroute.cafe24.com/product/detail.html?product_no=17</t>
-  </si>
-  <si>
-    <t>https://bellroute.cafe24.com/product/detail.html?product_no=80</t>
   </si>
   <si>
     <t>MTP0007</t>
@@ -550,33 +550,6 @@
     <t>https://bellroute.cafe24.com/product/detail.html?product_no=19</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Malgun Gothic"/>
-        <color rgb="FF000000"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve">상세페이지 </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="맑은 고딕"/>
-        <color rgb="FF000000"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>URL</t>
-    </r>
-  </si>
-  <si>
-    <t>UST0001</t>
-  </si>
-  <si>
-    <t>아노락세트 바스락셋업 여름 트레이닝 (4Color)</t>
-  </si>
-  <si>
-    <t>https://bellroute.cafe24.com/product/detail.html?product_no=41</t>
-  </si>
-  <si>
     <t>UTR0002</t>
   </si>
   <si>
@@ -651,6 +624,36 @@
   <si>
     <t>UTR0010</t>
   </si>
+  <si>
+    <t>1+1 여성 삥줄 사이드핀턱 와이드 벌룬팬츠 밴딩 바지</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Malgun Gothic"/>
+        <color rgb="FF000000"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t xml:space="preserve">상세페이지 </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="맑은 고딕"/>
+        <color rgb="FF000000"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t>URL</t>
+    </r>
+  </si>
+  <si>
+    <t>UST0001</t>
+  </si>
+  <si>
+    <t>아노락세트 바스락셋업 여름 트레이닝 (4Color)</t>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=41</t>
+  </si>
 </sst>
 </file>
 
@@ -719,7 +722,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
@@ -746,6 +749,9 @@
     </xf>
     <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1015,13 +1021,13 @@
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="2"/>
     </row>
@@ -1030,10 +1036,10 @@
         <v>18</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D3" s="2"/>
     </row>
@@ -1063,25 +1069,25 @@
     </row>
     <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D6" s="2"/>
     </row>
     <row r="7" ht="15.0" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D7" s="2"/>
     </row>
@@ -7087,18 +7093,18 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>129</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2" ht="17.25" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>132</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -12123,26 +12129,26 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" ht="17.25" customHeight="1">
+      <c r="A2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" ht="17.25" customHeight="1">
-      <c r="A2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="C2" s="4" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>23</v>
@@ -12183,13 +12189,13 @@
     </row>
     <row r="7" ht="17.25" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -17258,18 +17264,18 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" ht="17.25" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -17296,24 +17302,24 @@
     </row>
     <row r="5" ht="17.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -22322,18 +22328,18 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" ht="17.25" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -43576,97 +43582,99 @@
     </row>
     <row r="3" ht="17.25" customHeight="1">
       <c r="A3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4" ht="17.25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C4" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C3" s="4" t="s">
+    </row>
+    <row r="5" ht="17.25" customHeight="1">
+      <c r="A5" s="2" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="4" ht="17.25" customHeight="1">
-      <c r="A4" s="2" t="s">
+      <c r="B5" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C5" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="C4" s="4" t="s">
+    </row>
+    <row r="6" ht="17.25" customHeight="1">
+      <c r="A6" s="2" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="5" ht="17.25" customHeight="1">
-      <c r="A5" s="2" t="s">
+      <c r="B6" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C6" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="C5" s="4" t="s">
+    </row>
+    <row r="7" ht="17.25" customHeight="1">
+      <c r="A7" s="2" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="6" ht="17.25" customHeight="1">
-      <c r="A6" s="2" t="s">
+      <c r="B7" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C7" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="C6" s="4" t="s">
+    </row>
+    <row r="8" ht="17.25" customHeight="1">
+      <c r="A8" s="2" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="7" ht="17.25" customHeight="1">
-      <c r="A7" s="2" t="s">
+      <c r="B8" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C8" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="C7" s="4" t="s">
+    </row>
+    <row r="9" ht="17.25" customHeight="1">
+      <c r="A9" s="2" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="8" ht="17.25" customHeight="1">
-      <c r="A8" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C9" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="C8" s="4" t="s">
+    </row>
+    <row r="10" ht="17.25" customHeight="1">
+      <c r="A10" s="2" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="9" ht="17.25" customHeight="1">
-      <c r="A9" s="2" t="s">
+      <c r="B10" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C10" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="C9" s="4" t="s">
+    </row>
+    <row r="11" ht="17.25" customHeight="1">
+      <c r="A11" s="2" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="10" ht="17.25" customHeight="1">
-      <c r="A10" s="2" t="s">
+      <c r="B11" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="11" ht="17.25" customHeight="1">
-      <c r="A11" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="B11" s="2"/>
       <c r="C11" s="2"/>
     </row>
     <row r="12" ht="17.25" customHeight="1">
